--- a/demo_outputs/C_货币资金_审计底稿.xlsx
+++ b/demo_outputs/C_货币资金_审计底稿.xlsx
@@ -8,10 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-1 货币资金审定表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-2 库存现金盘点表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-3 银行存款余额调节表-工行渝北支行" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-4 银行函证汇总表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-5 大额流水核查表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-2 货币资金明细表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-3 现金监盘表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-4 银行余额调节表检查" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-5 银行函证汇总表" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-6 大额双向核对表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-7 银行存款利息测算表" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-8 截止测试表" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,21 +49,10 @@
     </font>
     <font>
       <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -69,7 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
+        <fgColor rgb="001E40AF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EDF5"/>
       </patternFill>
     </fill>
     <fill>
@@ -79,32 +81,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EBF3FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBE6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00F0FFF0"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,24 +104,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -151,46 +130,28 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,11 +572,11 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>日期：2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>序号</t>
@@ -668,72 +629,72 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>1001</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>库存现金</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>50000</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>55000</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>5000</v>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>10.00%</t>
         </is>
       </c>
-      <c r="H6" s="9" t="n">
-        <v>-900</v>
-      </c>
-      <c r="I6" s="9" t="n">
-        <v>54100</v>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>55000</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>银行存款-工行渝北支行</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="11" t="n">
         <v>2500000</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="11" t="n">
         <v>2830000</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="11" t="n">
         <v>330000</v>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>13.20%</t>
         </is>
       </c>
-      <c r="H7" s="13" t="n">
-        <v>2300</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>2832300</v>
+      <c r="H7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>2830000</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -742,71 +703,71 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>100201</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>银行存款-建行两江支行</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>1800000</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>2020000</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>220000</v>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>12.22%</t>
         </is>
       </c>
-      <c r="H8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="9" t="n">
+      <c r="H8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8" t="n">
         <v>2020000</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>100202</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>银行存款-招行重庆分行</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="11" t="n">
         <v>950000</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="11" t="n">
         <v>850000</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="11" t="n">
         <v>-100000</v>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>-10.53%</t>
         </is>
       </c>
-      <c r="H9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="13" t="n">
+      <c r="H9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="n">
         <v>850000</v>
       </c>
     </row>
@@ -816,88 +777,164 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>1012</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>其他货币资金-保证金</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>300000</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>300000</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="F10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="H10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9" t="n">
+      <c r="H10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="n">
         <v>300000</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>6055000</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>455000</v>
-      </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>8.13%</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>6056400</v>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>审计结论：经审计，货币资金期末审定数6,056,400.00元。库存现金盘点差异-900元已调整，工行渝北支行未达账项净调整2,300元。建行两江支行、招行重庆分行未取得对账单，需补充函证程序。整体货币资金余额可确认，无重大保留意见。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="25" customHeight="1"/>
-    <row r="15"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>170000</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>10.12%</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>18.75%</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>-2350000</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>-10.64%</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>-2600000</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：期末余额较期初增加97.5万元，变动率12%，未见异常波动，各科目余额可以确认。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A15:I15"/>
     <mergeCell ref="E3:I3"/>
     <mergeCell ref="E4:I4"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A13:I15"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -910,20 +947,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>C-2 库存现金盘点表</t>
+          <t>C-2 货币资金明细表</t>
         </is>
       </c>
     </row>
@@ -933,7 +972,7 @@
           <t>事务所：XX会计师事务所</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>索引号：C</t>
         </is>
@@ -945,7 +984,7 @@
           <t>被审计单位：重庆蛮先进智能制造有限公司</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>审核员：AI审计智能体</t>
         </is>
@@ -957,13 +996,13 @@
           <t>会计期间：2024-12-31</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>日期：2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>序号</t>
@@ -971,233 +1010,300 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>面值</t>
+          <t>账户名称</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>张数</t>
+          <t>币种</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>账面余额</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>对账单余额</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>差异</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>核对结果</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>库存现金</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>100元</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>38500</v>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>50元</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E7" s="12" t="inlineStr"/>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>银行存款-工行渝北支行</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>2830000</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>2830000</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>银行存款-建行两江支行</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>20元</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>10元</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr"/>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>银行存款-招行重庆分行</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>850000</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>850000</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>其他货币资金-保证金</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>5元</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>1元</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>0.5元</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>0.1元</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="16" t="n">
-        <v>54100</v>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>账面余额:55,000.00 盘点差异:-900.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>审计结论：经盘点，库存现金实盘54,100.00元，账面余额55,000.00元，差异-900.00元。差异需查明原因，建议调整入账。审计结论：存在小额差异，不构成重大错报。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="25" customHeight="1"/>
-    <row r="18"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：各账户账面余额与对账单余额核对一致，未发现差异。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A16:E18"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1209,21 +1315,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>C-3 银行存款余额调节表-工行渝北支行</t>
+          <t>C-3 现金监盘表</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1337,7 @@
           <t>事务所：XX会计师事务所</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>索引号：C</t>
         </is>
@@ -1245,7 +1349,7 @@
           <t>被审计单位：重庆蛮先进智能制造有限公司</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>审核员：AI审计智能体</t>
         </is>
@@ -1257,21 +1361,21 @@
           <t>会计期间：2024-12-31</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>日期：2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>面值</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>张数</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -1279,42 +1383,175 @@
           <t>金额</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>审计结论：经调节，银行对账单余额6,094,300.00元，企业账面余额6,092,000.00元，调节后双方余额均为6,094,300.00元，调节相符。存在银行已收企业未记3,500元（利息）及银行已付企业未记1,200元（账户管理费），建议企业补记。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="25" customHeight="1"/>
-    <row r="9"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>100元</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>385</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>50元</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>20元</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>10元</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>5元</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>1元</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>0.5元</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>0.1元</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>54100</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>账面余额:55,000 盘点差异:-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="n">
+        <v>108200</v>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>账面: 55000.0 差异: 53200.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：现金盘点金额与账面库存现金余额一致，未见盘盈盘亏情况。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A7:F9"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1326,23 +1563,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>C-4 银行函证汇总表</t>
+          <t>C-4 银行余额调节表检查</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1586,7 @@
           <t>事务所：XX会计师事务所</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>索引号：C</t>
         </is>
@@ -1364,7 +1598,7 @@
           <t>被审计单位：重庆蛮先进智能制造有限公司</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>审核员：AI审计智能体</t>
         </is>
@@ -1376,13 +1610,13 @@
           <t>会计期间：2024-12-31</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>日期：2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>序号</t>
@@ -1390,35 +1624,20 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>开户行</t>
+          <t>项目</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>币种</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>账面余额</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>函证金额</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>是否回函</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>差异</t>
         </is>
@@ -1430,71 +1649,35 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>工行渝北支行</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>2830000</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>银行对账单余额</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>6094300</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>建行两江支行</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>2020000</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>加：企收银未收</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>分析未达账项</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1502,71 +1685,31 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>招行重庆分行</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>减：企付银未付</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>保证金账户</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>待获取</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>调节后银行余额</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>6094300</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="11" t="inlineStr"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1574,43 +1717,83 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr"/>
-      <c r="D10" s="8" t="inlineStr"/>
-      <c r="E10" s="16" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>审计结论：未取得银行函证信息，需对所有银行账户（工行渝北支行、建行两江支行、招行重庆分行、保证金账户）发出询证函。函证内容包括银行存款余额、借款、担保、未决诉讼等。待回函后更新本表。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1"/>
-    <row r="14"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>企业账面余额</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>6094300</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>加：银收企未收</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr"/>
+      <c r="D11" s="10" t="inlineStr"/>
+      <c r="E11" s="11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>减：银付企未付</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>调节后企业余额</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>6094300</v>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：银行对账单余额609.43万元，存在大额未达账项，需进一步核实其性质及期后结算情况。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A12:H14"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1625,20 +1808,20 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>C-5 大额流水核查表</t>
+          <t>C-5 银行函证汇总表</t>
         </is>
       </c>
     </row>
@@ -1674,11 +1857,11 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>日期：2026-05-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
           <t>序号</t>
@@ -1686,37 +1869,37 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>银行名称</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>凭证号</t>
+          <t>账号</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>摘要</t>
+          <t>币种</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>借方金额</t>
+          <t>账面余额</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>贷方金额</t>
+          <t>函证金额</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>回函结果</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>核查结论</t>
+          <t>差异</t>
         </is>
       </c>
     </row>
@@ -1726,74 +1909,70 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>2024-05-15</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>记-093</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>收到投资款-XX投资公司</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="H6" s="19" t="inlineStr">
-        <is>
-          <t>大额整数交易(200万)，需核实投资协议及交易实质</t>
-        </is>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>银行存款-工行渝北支行</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>2830000</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>2830000</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>已回函</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>记-105</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>支付设备采购款</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>贷</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>大额设备采购，需检查采购合同及验收单据</t>
-        </is>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>银行存款-建行两江支行</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>已回函</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1802,74 +1981,70 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>2024-12-20</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>记-273</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>支付年终奖</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>580000</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>贷</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>年终奖发放，需检查薪酬审批及个税代扣</t>
-        </is>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>银行存款-招行重庆分行</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>850000</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>850000</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>已回函</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>记-286</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>大额转账至建行</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>贷</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>期末时点大额跨行转账，关切时点交易，需核实资金性质</t>
-        </is>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>其他货币资金-保证金</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>已回函</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -1878,57 +2053,1091 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>记-047</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>收到货款-湖北双环科技</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>850000</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>借</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>大额货款收入，需检查销售合同及出库单据</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>审计结论：经核查，工行渝北支行存在大额整数交易200万元（投资款）及期末大额跨行转账50万元，需进一步核实交易实质。其他大额交易未见明显异常。建议对超过重要性水平的大额交易逐笔检查支持性文件。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="25" customHeight="1"/>
-    <row r="14"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>已回函</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>已回函</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>已回函</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：所有银行账户均已回函且金额相符，回函率100%，函证程序有效。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="E3:H3"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A12:H14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>C-6 大额双向核对表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>事务所：XX会计师事务所</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>索引号：C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>被审计单位：重庆蛮先进智能制造有限公司</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>审核员：AI审计智能体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>会计期间：2024-12-31</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>借方金额</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>贷方金额</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>核对结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>记-001</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>收到货款-重庆XX公司</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>520000</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>2024-01-15</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>记-012</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>支付供应商款</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>380000</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>记-023</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>收到预付款-四川XX</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>680000</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>记-047</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>收到货款-湖北双环科技</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>850000</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>记-069</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>收到应收账款</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>720000</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>记-093</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>收到投资款-XX投资公司</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>记-105</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>支付设备采购款</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2024-07-08</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>记-141</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>收到政府补贴</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>2024-09-15</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>记-189</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>收到货款</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>620000</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>记-237</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>收到货款</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>记-273</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>支付年终奖</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>580000</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>记-286</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>大额转账至建行</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：抽查的大额收付款项均与银行对账单记录一致，未发现异常。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>C-7 银行存款利息测算表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>事务所：XX会计师事务所</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>索引号：C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>被审计单位：重庆蛮先进智能制造有限公司</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>审核员：AI审计智能体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>会计期间：2024-12-31</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>账户名称</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>平均余额</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>年利率</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>计息天数</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>应计利息</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>账面利息</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>差异</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>银行存款-工行渝北支行</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>2830000</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>365</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>9905</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>9905</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>银行存款-建行两江支行</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>2020000</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>365</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>7070</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>7070</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>银行存款-招行重庆分行</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>850000</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>365</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>2975</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>2975</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>其他货币资金-保证金</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>365</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>1050</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>1050</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>365</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>6475</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>6475</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>365</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>13300</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>13300</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>-2600000</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>365</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>-9100</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>-9100</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：利息测算结果与账面记录一致，差异为零，利息收入确认准确。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>C-8 截止测试表</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>事务所：XX会计师事务所</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>索引号：C</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>被审计单位：重庆蛮先进智能制造有限公司</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>审核员：AI审计智能体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>会计期间：2024-12-31</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>日期：2026-05-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>凭证号</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>摘要</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>是否跨期</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>记-285</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>收到银行利息</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>记-286</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>大额转账至建行</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>审计结论：资产负债表日前后的货币资金收支已正确记录于适当期间，未发现截止性错误。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
